--- a/WareTrack_game_rules.xlsx
+++ b/WareTrack_game_rules.xlsx
@@ -15,6 +15,8 @@
     <sheet name="Actions" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Upgrades" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="World and traffic" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Deliveries" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Delivery upgrades" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -48,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="256">
   <si>
     <t xml:space="preserve">Shift calculator</t>
   </si>
@@ -693,6 +695,129 @@
   </si>
   <si>
     <t xml:space="preserve">Zooms out to all five sites with a name pin over each</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery vans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every shipped order becomes a delivery to a shop. Credits go straight to your balance, in shifts and in free play.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How it works</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promised time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minutes from shipping until the drop is due: 25 + 3 per block of route (+5 with a Dispatcher)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base fee (credits)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 + 0.25 per block, then the route-planner and rating multipliers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Early drop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 or more minutes before the promised time: +25% tip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Late drop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After the promised time: half pay, and your rating drops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rating multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8 + 0.1 × rating (rating 0–5, starts at 4.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Running cost per trip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charged when a van leaves the depot (Electric vans: free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example fee (8 blocks, early, rating 4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base × rating × early tip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery staff and tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bought any time with credits from the Vans tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level 1 (cr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level 2 (cr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level 3 (cr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total (cr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery drivers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fleet of 3 vans, then 4, 5 and 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driver training</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vans drive 12% faster per level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dispatcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Most urgent job goes first; promises 5 min longer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handheld scanners</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drop-offs take half the time; +1 cr tip each</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Route planner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery fees +15% per level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bigger vans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each van carries 2 deliveries per trip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electric vans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trips cost nothing to run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everything bought</t>
   </si>
 </sst>
 </file>
@@ -2524,4 +2649,345 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <f aca="false">25+3*8</f>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <f aca="false">2+0.25*8</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <f aca="false">0.8+0.1*4</f>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <f aca="false">ROUND(C6*C9*C7,0)</f>
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>180</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>320</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <f aca="false">SUM(D5:F5)</f>
+        <v>590</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="F6" s="13"/>
+      <c r="G6" s="12" t="n">
+        <f aca="false">SUM(D6:F6)</f>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="12" t="n">
+        <f aca="false">SUM(D7:F7)</f>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="12" t="n">
+        <f aca="false">SUM(D8:F8)</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="F9" s="13"/>
+      <c r="G9" s="12" t="n">
+        <f aca="false">SUM(D9:F9)</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>160</v>
+      </c>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="12" t="n">
+        <f aca="false">SUM(D10:F10)</f>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="12" t="n">
+        <f aca="false">SUM(D11:F11)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <f aca="false">SUM(G5:G11)</f>
+        <v>1560</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/WareTrack_game_rules.xlsx
+++ b/WareTrack_game_rules.xlsx
@@ -709,7 +709,7 @@
     <t xml:space="preserve">Promised time</t>
   </si>
   <si>
-    <t xml:space="preserve">Minutes from shipping until the drop is due: 25 + 3 per block of route (+5 with a Dispatcher)</t>
+    <t xml:space="preserve">Minutes from shipping until the drop is due: 30 + 3 per block of route (+5 with a Dispatcher)</t>
   </si>
   <si>
     <t xml:space="preserve">Base fee (credits)</t>
@@ -2693,8 +2693,8 @@
         <v>219</v>
       </c>
       <c r="C5" s="12" t="n">
-        <f aca="false">25+3*8</f>
-        <v>49</v>
+        <f aca="false">30+3*8</f>
+        <v>54</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/WareTrack_game_rules.xlsx
+++ b/WareTrack_game_rules.xlsx
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="271">
   <si>
     <t xml:space="preserve">Shift calculator</t>
   </si>
@@ -697,6 +697,36 @@
     <t xml:space="preserve">Zooms out to all five sites with a name pin over each</t>
   </si>
   <si>
+    <t xml:space="preserve">Transfer trucks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WareTrack trucks drive stock between your warehouses on the public roads, obeying the same lights and lanes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every 90–160 min per site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request a transfer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock tab: a nearby warehouse sends 5 pallets (4 of the product you need). Slower than Expedite but cheaper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yard lane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One truck moves in a yard lane at a time: a truck only backs into a dock or pulls out when the lane is clear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approach roads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traffic enters and leaves the map along long approach roads, so vehicles never pop in or vanish on screen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Delivery vans</t>
   </si>
   <si>
@@ -746,6 +776,21 @@
   </si>
   <si>
     <t xml:space="preserve">Base × rating × early tip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every shop and every house in the city around the site you run: 8 shops and 10 homes per site, plus shops you build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 per site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipment tracking → Outbound follows an order: placed, picked, staged, shipped, out for delivery, delivered. Tap a shop or house to see its open orders</t>
   </si>
   <si>
     <t xml:space="preserve">Delivery staff and tools</t>
@@ -2477,7 +2522,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -2637,6 +2682,50 @@
         <v>214</v>
       </c>
       <c r="C16" s="12" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>212</v>
       </c>
     </row>
@@ -2656,7 +2745,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -2666,12 +2755,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2679,7 +2768,7 @@
         <v>180</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>181</v>
@@ -2687,10 +2776,10 @@
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C5" s="12" t="n">
         <f aca="false">30+3*8</f>
@@ -2699,10 +2788,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C6" s="12" t="n">
         <f aca="false">2+0.25*8</f>
@@ -2711,10 +2800,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>1.25</v>
@@ -2722,10 +2811,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>0.5</v>
@@ -2733,10 +2822,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="C9" s="12" t="n">
         <f aca="false">0.8+0.1*4</f>
@@ -2745,10 +2834,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>2</v>
@@ -2756,14 +2845,36 @@
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="C11" s="12" t="n">
         <f aca="false">ROUND(C6*C9*C7,0)</f>
         <v>6</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -2793,12 +2904,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2806,33 +2917,33 @@
         <v>165</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>150</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="D5" s="13" t="n">
         <v>90</v>
@@ -2850,13 +2961,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="D6" s="13" t="n">
         <v>70</v>
@@ -2872,13 +2983,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="D7" s="13" t="n">
         <v>110</v>
@@ -2892,13 +3003,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>60</v>
@@ -2912,13 +3023,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="D9" s="13" t="n">
         <v>100</v>
@@ -2934,13 +3045,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="D10" s="13" t="n">
         <v>160</v>
@@ -2954,13 +3065,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="D11" s="13" t="n">
         <v>120</v>
@@ -2974,7 +3085,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="G13" s="7" t="n">
         <f aca="false">SUM(G5:G11)</f>

--- a/WareTrack_game_rules.xlsx
+++ b/WareTrack_game_rules.xlsx
@@ -820,7 +820,7 @@
     <t xml:space="preserve">Staff</t>
   </si>
   <si>
-    <t xml:space="preserve">Fleet of 3 vans, then 4, 5 and 6</t>
+    <t xml:space="preserve">Fleet of 4 vans, then 5, 6 and 7</t>
   </si>
   <si>
     <t xml:space="preserve">Driver training</t>

--- a/WareTrack_game_rules.xlsx
+++ b/WareTrack_game_rules.xlsx
@@ -17,6 +17,7 @@
     <sheet name="World and traffic" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Deliveries" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="Delivery upgrades" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Challenge and rewards" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="305">
   <si>
     <t xml:space="preserve">Shift calculator</t>
   </si>
@@ -863,6 +864,108 @@
   </si>
   <si>
     <t xml:space="preserve">Everything bought</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order requests, Hands-on mode, missions and streaks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The systems that give each session a goal and a reason to come back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order request window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">During a shift every new order pops up in the Actions card. Accept, rush it or decline before the timer runs out (real seconds, paused when the game is paused)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missed request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The customer goes elsewhere: points lost and customer rating drops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rating cost of a missed request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied to the 0–5 customer rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rating cost of declining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Declining is cheaper than ignoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rush an order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accept as rush: due in 25 minutes, pays the rush bonus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Out-of-stock request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accepting sends a transfer truck from another warehouse automatically (15 points)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hands-on mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You dock every truck, release every order to the floor and send every van yourself; all points earned are multiplied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 active missions from 11 types (put-aways, on-time orders, deliveries, home drops, early drops, delivery credits, fast trucks, streaks, combos, transfers, 2-star shifts); targets and rewards grow with level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30–60 cr + XP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mission chest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every 5th mission completed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-time delivery streak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each consecutive on-time drop adds to every delivery fee; a late drop resets it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2.5% per drop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streak cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highest streak bonus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+25%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welcome-back pay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">While you are away your network keeps earning; counted for up to 8 hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 cr/h + upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North and South districts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 more homes per site, further out and better paid; open with the first Delivery drivers upgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5th van</t>
   </si>
 </sst>
 </file>
@@ -1552,6 +1655,194 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>304</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
